--- a/data/trans_orig/P0902-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47822</t>
+          <t>46886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45050</t>
+          <t>45187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75342</t>
+          <t>76249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237282</t>
+          <t>238785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257473</t>
+          <t>257521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213016</t>
+          <t>213952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235862</t>
+          <t>235944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458506</t>
+          <t>457599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488798</t>
+          <t>488661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61254</t>
+          <t>60462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66889</t>
+          <t>67800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100470</t>
+          <t>101364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107259</t>
+          <t>107170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149020</t>
+          <t>151465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431821</t>
+          <t>432613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458929</t>
+          <t>459466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>403479</t>
+          <t>402585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>437060</t>
+          <t>436149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>848004</t>
+          <t>845559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889765</t>
+          <t>889854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24074</t>
+          <t>23745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29242</t>
+          <t>29935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52302</t>
+          <t>53356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69936</t>
+          <t>71883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294772</t>
+          <t>295101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309641</t>
+          <t>310461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283110</t>
+          <t>282056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306170</t>
+          <t>305477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584322</t>
+          <t>582375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>612247</t>
+          <t>612737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40510</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67914</t>
+          <t>67699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51389</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82094</t>
+          <t>82636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335298</t>
+          <t>336454</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>350573</t>
+          <t>350751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>303757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330946</t>
+          <t>330743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>648033</t>
+          <t>647491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>678738</t>
+          <t>678404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51873</t>
+          <t>52423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179378</t>
+          <t>180222</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194294</t>
+          <t>194197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173270</t>
+          <t>172043</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191841</t>
+          <t>191963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>359103</t>
+          <t>358553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383002</t>
+          <t>381913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59326</t>
+          <t>58784</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54275</t>
+          <t>54054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84177</t>
+          <t>83633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239227</t>
+          <t>238880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256345</t>
+          <t>256415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218818</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243930</t>
+          <t>243725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>464778</t>
+          <t>465322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494680</t>
+          <t>494901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43554</t>
+          <t>43694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72363</t>
+          <t>74107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68095</t>
+          <t>68342</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102759</t>
+          <t>103740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123108</t>
+          <t>121272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168490</t>
+          <t>163652</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>542664</t>
+          <t>540920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>571473</t>
+          <t>571333</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>535460</t>
+          <t>534479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>570124</t>
+          <t>569877</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1084756</t>
+          <t>1089594</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1130138</t>
+          <t>1131974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>62099</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92301</t>
+          <t>93722</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106390</t>
+          <t>108509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>149148</t>
+          <t>152395</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>176582</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231784</t>
+          <t>230336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>651494</t>
+          <t>650073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>682019</t>
+          <t>681696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>634363</t>
+          <t>631116</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>677121</t>
+          <t>675002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1295522</t>
+          <t>1296970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1346150</t>
+          <t>1350724</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238988</t>
+          <t>238484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>302230</t>
+          <t>303784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>451936</t>
+          <t>452227</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>535285</t>
+          <t>533460</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>713886</t>
+          <t>711231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>816233</t>
+          <t>815883</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2974313</t>
+          <t>2972759</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3037555</t>
+          <t>3038059</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2843912</t>
+          <t>2845737</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2927261</t>
+          <t>2926970</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5839508</t>
+          <t>5839858</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5941855</t>
+          <t>5944510</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52026</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62864</t>
+          <t>62590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94164</t>
+          <t>94050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98947</t>
+          <t>98150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138724</t>
+          <t>138744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242712</t>
+          <t>242569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266401</t>
+          <t>266294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193081</t>
+          <t>193195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224381</t>
+          <t>224655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443259</t>
+          <t>443239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483036</t>
+          <t>483833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71718</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79825</t>
+          <t>79516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115528</t>
+          <t>115519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122604</t>
+          <t>127964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173244</t>
+          <t>176749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433809</t>
+          <t>433192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>465664</t>
+          <t>464372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>408237</t>
+          <t>408246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443940</t>
+          <t>444249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>856048</t>
+          <t>852543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>906688</t>
+          <t>901328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51937</t>
+          <t>52210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45097</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74158</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78700</t>
+          <t>80340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117761</t>
+          <t>117951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272109</t>
+          <t>271836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297027</t>
+          <t>297755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266862</t>
+          <t>266843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295923</t>
+          <t>294999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547305</t>
+          <t>547115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>586366</t>
+          <t>584726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>42986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74340</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106622</t>
+          <t>106686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143846</t>
+          <t>145118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157678</t>
+          <t>157680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203608</t>
+          <t>205541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>299642</t>
+          <t>301982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330876</t>
+          <t>330996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>245105</t>
+          <t>243833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282329</t>
+          <t>282265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>559325</t>
+          <t>557392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>605255</t>
+          <t>605253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34520</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45744</t>
+          <t>45942</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72657</t>
+          <t>72525</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68993</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101508</t>
+          <t>101424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178098</t>
+          <t>177966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196318</t>
+          <t>196453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146934</t>
+          <t>147066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173847</t>
+          <t>173649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330701</t>
+          <t>330785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363216</t>
+          <t>363793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>25137</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34321</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59828</t>
+          <t>61569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64590</t>
+          <t>66232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100088</t>
+          <t>98721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227763</t>
+          <t>227355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249346</t>
+          <t>248844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>220203</t>
+          <t>218462</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245710</t>
+          <t>244336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>453924</t>
+          <t>455291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>489422</t>
+          <t>487780</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35564</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63022</t>
+          <t>63078</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87431</t>
+          <t>86360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125756</t>
+          <t>127409</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128999</t>
+          <t>129634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180925</t>
+          <t>177902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598845</t>
+          <t>598789</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>626303</t>
+          <t>626048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>566185</t>
+          <t>564532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>604510</t>
+          <t>605581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1172883</t>
+          <t>1175906</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1224809</t>
+          <t>1224174</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65534</t>
+          <t>64912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102914</t>
+          <t>101842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119251</t>
+          <t>119509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162984</t>
+          <t>165906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>198228</t>
+          <t>195451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>254977</t>
+          <t>253294</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>676184</t>
+          <t>677256</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>713564</t>
+          <t>714186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>658836</t>
+          <t>655914</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>702569</t>
+          <t>702311</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1345941</t>
+          <t>1347624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1402690</t>
+          <t>1405467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>341647</t>
+          <t>338801</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>417602</t>
+          <t>417786</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>665859</t>
+          <t>662615</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>756351</t>
+          <t>760522</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1019635</t>
+          <t>1031353</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1146997</t>
+          <t>1146398</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3008256</t>
+          <t>3008072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3084211</t>
+          <t>3087057</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2798012</t>
+          <t>2793841</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2888504</t>
+          <t>2891748</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5833225</t>
+          <t>5833824</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5960587</t>
+          <t>5948869</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56815</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87882</t>
+          <t>88202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84431</t>
+          <t>83730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125228</t>
+          <t>122188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249700</t>
+          <t>249879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272364</t>
+          <t>272329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200821</t>
+          <t>200501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231888</t>
+          <t>231267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>457236</t>
+          <t>460276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498033</t>
+          <t>498734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>53985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61109</t>
+          <t>62295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97222</t>
+          <t>96097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>98972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143695</t>
+          <t>143151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447137</t>
+          <t>448590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471598</t>
+          <t>472530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425862</t>
+          <t>426987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461975</t>
+          <t>460789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>881964</t>
+          <t>882508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926630</t>
+          <t>926687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>51033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46942</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77816</t>
+          <t>77927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285617</t>
+          <t>284850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302939</t>
+          <t>302679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>285276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>311254</t>
+          <t>309981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>577058</t>
+          <t>576947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>607932</t>
+          <t>607941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47441</t>
+          <t>48045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76472</t>
+          <t>77266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97170</t>
+          <t>98306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134966</t>
+          <t>137161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151389</t>
+          <t>153066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203040</t>
+          <t>204401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293492</t>
+          <t>292698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322523</t>
+          <t>321919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>252317</t>
+          <t>250122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290113</t>
+          <t>288977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554207</t>
+          <t>552846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>605858</t>
+          <t>604181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25489</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>41589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35252</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>62116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185732</t>
+          <t>185746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201719</t>
+          <t>201369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178305</t>
+          <t>176998</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198148</t>
+          <t>197063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368783</t>
+          <t>367692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394556</t>
+          <t>394300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50178</t>
+          <t>48942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72302</t>
+          <t>71913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77380</t>
+          <t>76929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113609</t>
+          <t>114544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212945</t>
+          <t>214181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235753</t>
+          <t>236149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200813</t>
+          <t>201202</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>230274</t>
+          <t>228778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>422629</t>
+          <t>421694</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>458858</t>
+          <t>459309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42857</t>
+          <t>42663</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74666</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108621</t>
+          <t>110458</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155281</t>
+          <t>155514</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>162751</t>
+          <t>161652</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215997</t>
+          <t>215603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>581892</t>
+          <t>584216</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613701</t>
+          <t>613895</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>536013</t>
+          <t>535780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>582673</t>
+          <t>580836</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1131855</t>
+          <t>1132249</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1185101</t>
+          <t>1186200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33572</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>61410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86454</t>
+          <t>86155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129966</t>
+          <t>127868</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>128206</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180614</t>
+          <t>178774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>718366</t>
+          <t>717173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>745011</t>
+          <t>744458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696201</t>
+          <t>698299</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>739713</t>
+          <t>740012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1424136</t>
+          <t>1425976</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1474013</t>
+          <t>1476544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>281101</t>
+          <t>283906</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>349067</t>
+          <t>351962</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>584959</t>
+          <t>582595</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>680069</t>
+          <t>673586</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>884783</t>
+          <t>884720</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1002133</t>
+          <t>1001150</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3045283</t>
+          <t>3042388</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3113249</t>
+          <t>3110444</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2864473</t>
+          <t>2870956</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2959583</t>
+          <t>2961947</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5936759</t>
+          <t>5937742</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6054109</t>
+          <t>6054172</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35206</t>
+          <t>36069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70673</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276237</t>
+          <t>275374</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296002</t>
+          <t>295172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248050</t>
+          <t>247677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264154</t>
+          <t>264158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>530404</t>
+          <t>529437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556442</t>
+          <t>555414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72125</t>
+          <t>69939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108983</t>
+          <t>109316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109432</t>
+          <t>110831</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141337</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190781</t>
+          <t>188850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242220</t>
+          <t>237897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409407</t>
+          <t>409074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446265</t>
+          <t>448451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373632</t>
+          <t>372462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>405537</t>
+          <t>404138</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>791139</t>
+          <t>795462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>842578</t>
+          <t>844509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54412</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50271</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74165</t>
+          <t>73729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88935</t>
+          <t>87648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119772</t>
+          <t>119806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>261638</t>
+          <t>260679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283909</t>
+          <t>283470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274329</t>
+          <t>274765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298223</t>
+          <t>297944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>544773</t>
+          <t>544739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>575610</t>
+          <t>576897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42759</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71709</t>
+          <t>71664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123239</t>
+          <t>124893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108982</t>
+          <t>110833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183462</t>
+          <t>179810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240277</t>
+          <t>240322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269227</t>
+          <t>269501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352479</t>
+          <t>350825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>416972</t>
+          <t>418581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>604242</t>
+          <t>607894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>678722</t>
+          <t>676871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29655</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46092</t>
+          <t>45528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159297</t>
+          <t>159833</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170394</t>
+          <t>170392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176391</t>
+          <t>176393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188711</t>
+          <t>188179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339829</t>
+          <t>340393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356266</t>
+          <t>355474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48155</t>
+          <t>48709</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58530</t>
+          <t>59017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81873</t>
+          <t>82387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230782</t>
+          <t>230453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247816</t>
+          <t>246730</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208901</t>
+          <t>208347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>224790</t>
+          <t>224517</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>444819</t>
+          <t>444305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468162</t>
+          <t>467675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62288</t>
+          <t>61650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95132</t>
+          <t>96107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72311</t>
+          <t>61935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187306</t>
+          <t>189343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130272</t>
+          <t>130631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>260616</t>
+          <t>259319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>527277</t>
+          <t>526302</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560121</t>
+          <t>560759</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>661959</t>
+          <t>659922</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>776954</t>
+          <t>787330</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1211058</t>
+          <t>1212355</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341402</t>
+          <t>1341043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114480</t>
+          <t>114698</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128496</t>
+          <t>127786</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>164187</t>
+          <t>163507</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132669</t>
+          <t>136551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271383</t>
+          <t>275235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>814240</t>
+          <t>814022</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>895438</t>
+          <t>892677</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>553544</t>
+          <t>554224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>589235</t>
+          <t>589945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1375069</t>
+          <t>1371217</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1513783</t>
+          <t>1509901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>321017</t>
+          <t>311360</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>460924</t>
+          <t>457551</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>528351</t>
+          <t>539522</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>724086</t>
+          <t>725184</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>929269</t>
+          <t>943159</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1153476</t>
+          <t>1167569</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2995949</t>
+          <t>2999322</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3135856</t>
+          <t>3145513</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2936464</t>
+          <t>2935366</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3132199</t>
+          <t>3121028</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5963947</t>
+          <t>5949854</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6188154</t>
+          <t>6174264</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0902-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46886</t>
+          <t>47829</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>44977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76249</t>
+          <t>74129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238785</t>
+          <t>238548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257521</t>
+          <t>257484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213952</t>
+          <t>213009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235944</t>
+          <t>235621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>457599</t>
+          <t>459719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488661</t>
+          <t>488871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>33701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60462</t>
+          <t>60713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67800</t>
+          <t>67340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101364</t>
+          <t>98024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107170</t>
+          <t>108624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151465</t>
+          <t>149488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432613</t>
+          <t>432362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459466</t>
+          <t>459374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>402585</t>
+          <t>405925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436149</t>
+          <t>436609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>845559</t>
+          <t>847536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889854</t>
+          <t>888400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23745</t>
+          <t>24947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29935</t>
+          <t>28220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53356</t>
+          <t>53610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>42241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71883</t>
+          <t>69690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295101</t>
+          <t>293899</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310461</t>
+          <t>310183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282056</t>
+          <t>281802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305477</t>
+          <t>307192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>582375</t>
+          <t>584568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>612737</t>
+          <t>612017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>41562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67699</t>
+          <t>68254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>52570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82636</t>
+          <t>83886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336454</t>
+          <t>335701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>350751</t>
+          <t>350475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>303757</t>
+          <t>303202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330743</t>
+          <t>329894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>647491</t>
+          <t>646241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>678404</t>
+          <t>677557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>23301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52423</t>
+          <t>50563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180222</t>
+          <t>180007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194197</t>
+          <t>194185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172043</t>
+          <t>172920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191963</t>
+          <t>192677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>358553</t>
+          <t>360413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381913</t>
+          <t>383569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58784</t>
+          <t>59063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +2498,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>67919</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>54416</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>85584</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>12,37%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>67919</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>54054</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>83633</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>12,37%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238880</t>
+          <t>238030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256415</t>
+          <t>255701</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>219081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243725</t>
+          <t>243316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +2611,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>87,48%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>481036</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>463371</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>494539</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>87,63%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>481036</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>465322</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>494901</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>87,63%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43694</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74107</t>
+          <t>72781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>69246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103740</t>
+          <t>102220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121272</t>
+          <t>119755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163652</t>
+          <t>163588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>540920</t>
+          <t>542246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>571333</t>
+          <t>571967</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>534479</t>
+          <t>535999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>569877</t>
+          <t>568973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1089594</t>
+          <t>1089658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1131974</t>
+          <t>1133491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62099</t>
+          <t>60407</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93722</t>
+          <t>92175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108509</t>
+          <t>108710</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152395</t>
+          <t>151183</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176582</t>
+          <t>178885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>230336</t>
+          <t>231682</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>650073</t>
+          <t>651620</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>681696</t>
+          <t>683388</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>631116</t>
+          <t>632328</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>675002</t>
+          <t>674801</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1296970</t>
+          <t>1295624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1350724</t>
+          <t>1348421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238484</t>
+          <t>239433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>303784</t>
+          <t>300171</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>452227</t>
+          <t>453785</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>533460</t>
+          <t>535608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>711231</t>
+          <t>712708</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>815883</t>
+          <t>815514</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2972759</t>
+          <t>2976372</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3038059</t>
+          <t>3037110</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2845737</t>
+          <t>2843589</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2926970</t>
+          <t>2925412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5839858</t>
+          <t>5840227</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5944510</t>
+          <t>5943033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28444</t>
+          <t>28219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>52326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62590</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94050</t>
+          <t>94898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98150</t>
+          <t>95187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138744</t>
+          <t>138487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242569</t>
+          <t>242412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266294</t>
+          <t>266519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193195</t>
+          <t>192347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224655</t>
+          <t>223534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443239</t>
+          <t>443496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483833</t>
+          <t>486796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72335</t>
+          <t>70933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79516</t>
+          <t>77762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115519</t>
+          <t>116622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127964</t>
+          <t>126911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176749</t>
+          <t>174317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433192</t>
+          <t>434594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>464372</t>
+          <t>465803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>408246</t>
+          <t>407143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444249</t>
+          <t>446003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>852543</t>
+          <t>854975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901328</t>
+          <t>902381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>27252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52210</t>
+          <t>51327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46021</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74177</t>
+          <t>74320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80340</t>
+          <t>77376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117951</t>
+          <t>115898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271836</t>
+          <t>272719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297755</t>
+          <t>296794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266843</t>
+          <t>266700</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>294999</t>
+          <t>296406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547115</t>
+          <t>549168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584726</t>
+          <t>587690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>43982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>72795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106686</t>
+          <t>106960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145118</t>
+          <t>144691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157680</t>
+          <t>158249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205541</t>
+          <t>204306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>301982</t>
+          <t>301187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330996</t>
+          <t>330000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243833</t>
+          <t>244260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282265</t>
+          <t>281991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>557392</t>
+          <t>558627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>605253</t>
+          <t>604684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34652</t>
+          <t>35441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45942</t>
+          <t>47330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72525</t>
+          <t>72787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68416</t>
+          <t>68431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101424</t>
+          <t>100390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177966</t>
+          <t>177177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196453</t>
+          <t>195970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147066</t>
+          <t>146804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173649</t>
+          <t>172261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330785</t>
+          <t>331819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363793</t>
+          <t>363778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>25877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>47479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>34722</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61569</t>
+          <t>59377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>64647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98721</t>
+          <t>99418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227355</t>
+          <t>226502</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248844</t>
+          <t>248104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218462</t>
+          <t>220654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244336</t>
+          <t>245309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455291</t>
+          <t>454594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>487780</t>
+          <t>489365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35819</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63078</t>
+          <t>63298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86360</t>
+          <t>86296</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127409</t>
+          <t>123374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129634</t>
+          <t>126445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177902</t>
+          <t>178885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598789</t>
+          <t>598569</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>626048</t>
+          <t>625941</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>564532</t>
+          <t>568567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>605581</t>
+          <t>605645</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1175906</t>
+          <t>1174923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1224174</t>
+          <t>1227363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64912</t>
+          <t>62825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101842</t>
+          <t>101466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119509</t>
+          <t>121169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165906</t>
+          <t>164571</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>195451</t>
+          <t>196037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>253294</t>
+          <t>253415</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>677256</t>
+          <t>677632</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>714186</t>
+          <t>716273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>655914</t>
+          <t>657249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>702311</t>
+          <t>700651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1347624</t>
+          <t>1347503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1405467</t>
+          <t>1404881</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>338801</t>
+          <t>338802</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>417786</t>
+          <t>417195</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>662615</t>
+          <t>659330</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>760522</t>
+          <t>755598</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1025490</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1146398</t>
+          <t>1146875</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3008072</t>
+          <t>3008663</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3087057</t>
+          <t>3087056</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2793841</t>
+          <t>2798765</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2891748</t>
+          <t>2895033</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5833824</t>
+          <t>5833347</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5948869</t>
+          <t>5954732</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>44205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57436</t>
+          <t>56632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88202</t>
+          <t>87095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83730</t>
+          <t>83424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122188</t>
+          <t>122195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249879</t>
+          <t>249556</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272329</t>
+          <t>272442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200501</t>
+          <t>201608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231267</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460276</t>
+          <t>460269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498734</t>
+          <t>499040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30045</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>56188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62295</t>
+          <t>62340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96097</t>
+          <t>98144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98972</t>
+          <t>100302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143151</t>
+          <t>140886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448590</t>
+          <t>446387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472530</t>
+          <t>472020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426987</t>
+          <t>424940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460789</t>
+          <t>460744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>882508</t>
+          <t>884773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926687</t>
+          <t>925357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33715</t>
+          <t>34401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26328</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51033</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>46028</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77927</t>
+          <t>78304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284850</t>
+          <t>284164</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302679</t>
+          <t>302876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285276</t>
+          <t>286048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309981</t>
+          <t>309856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576947</t>
+          <t>576570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>607941</t>
+          <t>608846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48045</t>
+          <t>48128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77266</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98306</t>
+          <t>98233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>137612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153066</t>
+          <t>154390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204401</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292698</t>
+          <t>292694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321919</t>
+          <t>321836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250122</t>
+          <t>249671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288977</t>
+          <t>289050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>552846</t>
+          <t>554639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>604181</t>
+          <t>602857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>40273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>35612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62116</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185746</t>
+          <t>185788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201369</t>
+          <t>201821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176998</t>
+          <t>178314</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197063</t>
+          <t>198037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367692</t>
+          <t>369836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394300</t>
+          <t>394196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48942</t>
+          <t>49358</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44337</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71913</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76929</t>
+          <t>76609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114544</t>
+          <t>113931</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214181</t>
+          <t>213765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236149</t>
+          <t>235703</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201202</t>
+          <t>200332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228778</t>
+          <t>228149</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>421694</t>
+          <t>422307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>459309</t>
+          <t>459629</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>42643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>73258</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110458</t>
+          <t>110746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155514</t>
+          <t>154352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161652</t>
+          <t>162764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215603</t>
+          <t>215583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584216</t>
+          <t>583300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613895</t>
+          <t>613915</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>535780</t>
+          <t>536942</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>580836</t>
+          <t>580548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1132249</t>
+          <t>1132269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1186200</t>
+          <t>1185088</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>34333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61410</t>
+          <t>60401</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86155</t>
+          <t>82950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127868</t>
+          <t>126591</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128206</t>
+          <t>128225</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178774</t>
+          <t>178636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>717173</t>
+          <t>718182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>744458</t>
+          <t>744250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>698299</t>
+          <t>699576</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>740012</t>
+          <t>743217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1425976</t>
+          <t>1426114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1476544</t>
+          <t>1476525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>283906</t>
+          <t>282523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>351962</t>
+          <t>350229</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>582595</t>
+          <t>578553</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>673586</t>
+          <t>679771</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>884720</t>
+          <t>877351</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1001150</t>
+          <t>1003038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3042388</t>
+          <t>3044121</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3110444</t>
+          <t>3111827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2870956</t>
+          <t>2864771</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2961947</t>
+          <t>2965989</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5937742</t>
+          <t>5935854</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6054172</t>
+          <t>6061541</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>33459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>60476</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>48758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71640</t>
+          <t>75005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>287171</t>
+          <t>295403</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275374</t>
+          <t>285386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295172</t>
+          <t>302691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>257179</t>
+          <t>279026</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247677</t>
+          <t>268372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264158</t>
+          <t>286848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>544349</t>
+          <t>574430</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529437</t>
+          <t>559901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555414</t>
+          <t>586148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88501</t>
+          <t>93509</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>75129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109316</t>
+          <t>114288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125597</t>
+          <t>130655</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110831</t>
+          <t>113884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142507</t>
+          <t>148607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>214098</t>
+          <t>224165</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188850</t>
+          <t>198024</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237897</t>
+          <t>252351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>429889</t>
+          <t>437138</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409074</t>
+          <t>416359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448451</t>
+          <t>455518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>389372</t>
+          <t>415839</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372462</t>
+          <t>397887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>404138</t>
+          <t>432610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>819261</t>
+          <t>852976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>795462</t>
+          <t>824790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>844509</t>
+          <t>879117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32580</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55371</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61508</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50550</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73729</t>
+          <t>72166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>103701</t>
+          <t>102157</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87648</t>
+          <t>86952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119806</t>
+          <t>117411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273857</t>
+          <t>275014</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>260679</t>
+          <t>262961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283470</t>
+          <t>284172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>286986</t>
+          <t>294560</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274765</t>
+          <t>283571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>297944</t>
+          <t>304893</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>560844</t>
+          <t>569574</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>544739</t>
+          <t>554320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>576897</t>
+          <t>584779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>355737</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>355737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>355737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664545</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664545</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664545</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>62945</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71664</t>
+          <t>82404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>104992</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>88839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124893</t>
+          <t>121358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>151642</t>
+          <t>167938</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110833</t>
+          <t>146645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179810</t>
+          <t>193633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>256010</t>
+          <t>309614</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240322</t>
+          <t>290155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269501</t>
+          <t>323976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>380052</t>
+          <t>316969</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350825</t>
+          <t>300603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>418581</t>
+          <t>333122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>636062</t>
+          <t>626582</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>607894</t>
+          <t>600887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>676871</t>
+          <t>647875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787704</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787704</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787704</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>13197</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37406</t>
+          <t>39749</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>32224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45528</t>
+          <t>48249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165957</t>
+          <t>191975</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159833</t>
+          <t>185053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170392</t>
+          <t>196312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>182558</t>
+          <t>199618</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176393</t>
+          <t>192617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188179</t>
+          <t>205175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>348515</t>
+          <t>391593</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>340393</t>
+          <t>383093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355474</t>
+          <t>399118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207682</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207682</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207682</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385921</t>
+          <t>431342</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385921</t>
+          <t>431342</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385921</t>
+          <t>431342</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>29438</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39821</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32539</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>49459</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>69728</t>
+          <t>70014</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59017</t>
+          <t>58606</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82387</t>
+          <t>81976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239729</t>
+          <t>241269</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230453</t>
+          <t>232521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246730</t>
+          <t>248893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>217235</t>
+          <t>223174</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208347</t>
+          <t>214291</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>224517</t>
+          <t>231124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>456964</t>
+          <t>464443</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>444305</t>
+          <t>452481</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467675</t>
+          <t>475851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>77458</t>
+          <t>87691</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61650</t>
+          <t>71305</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96107</t>
+          <t>107601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>138579</t>
+          <t>171725</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>152868</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189343</t>
+          <t>192138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>216037</t>
+          <t>259416</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>235047</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>259319</t>
+          <t>287773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>544951</t>
+          <t>629889</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526302</t>
+          <t>609979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560759</t>
+          <t>646275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>710686</t>
+          <t>600332</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>659922</t>
+          <t>579919</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>787330</t>
+          <t>619189</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1255637</t>
+          <t>1230221</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1212355</t>
+          <t>1201864</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341043</t>
+          <t>1254590</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622409</t>
+          <t>717580</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622409</t>
+          <t>717580</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622409</t>
+          <t>717580</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471674</t>
+          <t>1489637</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471674</t>
+          <t>1489637</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471674</t>
+          <t>1489637</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>78915</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36043</t>
+          <t>73193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114698</t>
+          <t>109311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>144776</t>
+          <t>161537</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127786</t>
+          <t>143475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>163507</t>
+          <t>181644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>223691</t>
+          <t>250451</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136551</t>
+          <t>226634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275235</t>
+          <t>277461</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>849805</t>
+          <t>709158</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>814022</t>
+          <t>688761</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>892677</t>
+          <t>724879</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>572955</t>
+          <t>669794</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>554224</t>
+          <t>649687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>589945</t>
+          <t>687856</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1422761</t>
+          <t>1378952</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1371217</t>
+          <t>1351942</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1509901</t>
+          <t>1402769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>311360</t>
+          <t>402461</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>457551</t>
+          <t>481057</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>663528</t>
+          <t>734249</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>539522</t>
+          <t>694929</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>725184</t>
+          <t>774617</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1073033</t>
+          <t>1174366</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>943159</t>
+          <t>1116300</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1167569</t>
+          <t>1233820</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3047368</t>
+          <t>3089460</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2999322</t>
+          <t>3048519</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3145513</t>
+          <t>3127115</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2997022</t>
+          <t>2999314</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2935366</t>
+          <t>2958946</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3121028</t>
+          <t>3038634</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6044390</t>
+          <t>6088773</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5949854</t>
+          <t>6029319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6174264</t>
+          <t>6146839</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
